--- a/booking_forms/018_thesis_examination_scheduling_form--booking_forms.xlsx
+++ b/booking_forms/018_thesis_examination_scheduling_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
